--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487043_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487043_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.7642</v>
+        <v>6.6294</v>
       </c>
       <c r="E2" t="n">
-        <v>5.0135</v>
+        <v>5.1731</v>
       </c>
       <c r="F2" t="n">
-        <v>1.7507</v>
+        <v>1.4562</v>
       </c>
       <c r="G2" t="n">
         <v>6.5836</v>
@@ -610,13 +610,13 @@
         <v>2.7021</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6365</v>
+        <v>0.5017</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.2842</v>
+        <v>-0.1246</v>
       </c>
       <c r="U2" t="n">
-        <v>0.9207</v>
+        <v>0.6263</v>
       </c>
       <c r="V2" t="n">
         <v>-1.228</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.5475</v>
+        <v>3.3938</v>
       </c>
       <c r="E3" t="n">
-        <v>2.2206</v>
+        <v>2.1205</v>
       </c>
       <c r="F3" t="n">
-        <v>1.3269</v>
+        <v>1.2733</v>
       </c>
       <c r="G3" t="n">
         <v>3.4031</v>
@@ -688,13 +688,13 @@
         <v>2.3161</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3953</v>
+        <v>0.2416</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0727</v>
+        <v>-0.0274</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3225</v>
+        <v>0.269</v>
       </c>
       <c r="V3" t="n">
         <v>0.3281</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.2952</v>
+        <v>1.7935</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7621</v>
+        <v>0.662</v>
       </c>
       <c r="F4" t="n">
-        <v>1.5331</v>
+        <v>1.1316</v>
       </c>
       <c r="G4" t="n">
         <v>0.3629</v>
@@ -766,13 +766,13 @@
         <v>2.7021</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1329</v>
+        <v>-0.6345</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2842</v>
+        <v>-0.3843</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1513</v>
+        <v>-0.2502</v>
       </c>
       <c r="V4" t="n">
         <v>0.3281</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>I. VICUÑA ROYO</t>
+          <t>P. OSES TOME</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5344</v>
+        <v>1.3369</v>
       </c>
       <c r="E5" t="n">
-        <v>1.4608</v>
+        <v>1.0728</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0735</v>
+        <v>0.2641</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8471</v>
+        <v>-1.4933</v>
       </c>
       <c r="H5" t="n">
-        <v>1.2213</v>
+        <v>1.537</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3742</v>
+        <v>-3.0303</v>
       </c>
       <c r="J5" t="n">
-        <v>2.3282</v>
+        <v>0.9021</v>
       </c>
       <c r="K5" t="n">
-        <v>2.0026</v>
+        <v>2.6857</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3256</v>
+        <v>-1.7836</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.4811</v>
+        <v>-2.3954</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.7813</v>
+        <v>-1.1487</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.6998</v>
+        <v>-1.2467</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.9301</v>
+        <v>-1.158</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.8951</v>
+        <v>-3.8602</v>
       </c>
       <c r="R5" t="n">
-        <v>0.965</v>
+        <v>2.7021</v>
       </c>
       <c r="S5" t="n">
-        <v>1.3894</v>
+        <v>-0.2674</v>
       </c>
       <c r="T5" t="n">
-        <v>0.7998</v>
+        <v>-0.2247</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5896</v>
+        <v>-0.0427</v>
       </c>
       <c r="V5" t="n">
-        <v>1.228</v>
+        <v>4.2556</v>
       </c>
       <c r="W5" t="n">
-        <v>1.228</v>
+        <v>4.2556</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P. OSES TOME</t>
+          <t>M. BIDAURRE SOLA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.4172</v>
+        <v>1.0396</v>
       </c>
       <c r="E6" t="n">
-        <v>1.0728</v>
+        <v>2.6504</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3444</v>
+        <v>-1.6109</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.4933</v>
+        <v>2.724</v>
       </c>
       <c r="H6" t="n">
-        <v>1.537</v>
+        <v>-1.5659</v>
       </c>
       <c r="I6" t="n">
-        <v>-3.0303</v>
+        <v>4.2898</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9021</v>
+        <v>4.3858</v>
       </c>
       <c r="K6" t="n">
-        <v>2.6857</v>
+        <v>-0.1968</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.7836</v>
+        <v>4.5826</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.3954</v>
+        <v>-1.6619</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.1487</v>
+        <v>-1.3691</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.2467</v>
+        <v>-0.2928</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.158</v>
+        <v>0.965</v>
       </c>
       <c r="Q6" t="n">
-        <v>-3.8602</v>
+        <v>-0.965</v>
       </c>
       <c r="R6" t="n">
-        <v>2.7021</v>
+        <v>1.9301</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1871</v>
+        <v>-1.4215</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2247</v>
+        <v>-0.7704</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0377</v>
+        <v>-0.6511</v>
       </c>
       <c r="V6" t="n">
-        <v>4.2556</v>
+        <v>-1.228</v>
       </c>
       <c r="W6" t="n">
-        <v>4.2556</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. BIDAURRE SOLA</t>
+          <t>I. VICUÑA ROYO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6856</v>
+        <v>0.9395</v>
       </c>
       <c r="E7" t="n">
-        <v>2.35</v>
+        <v>0.9195</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.6644</v>
+        <v>0.02</v>
       </c>
       <c r="G7" t="n">
-        <v>2.724</v>
+        <v>0.8471</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.5659</v>
+        <v>1.2213</v>
       </c>
       <c r="I7" t="n">
-        <v>4.2898</v>
+        <v>-0.3742</v>
       </c>
       <c r="J7" t="n">
-        <v>4.3858</v>
+        <v>2.3282</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.1968</v>
+        <v>2.0026</v>
       </c>
       <c r="L7" t="n">
-        <v>4.5826</v>
+        <v>0.3256</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.6619</v>
+        <v>-1.4811</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.3691</v>
+        <v>-0.7813</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.2928</v>
+        <v>-0.6998</v>
       </c>
       <c r="P7" t="n">
+        <v>-1.9301</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>-2.8951</v>
+      </c>
+      <c r="R7" t="n">
         <v>0.965</v>
       </c>
-      <c r="Q7" t="n">
-        <v>-0.965</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.9301</v>
-      </c>
       <c r="S7" t="n">
-        <v>-1.7754</v>
+        <v>0.7945</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.0708</v>
+        <v>0.2585</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.7046</v>
+        <v>0.536</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.228</v>
+        <v>1.228</v>
       </c>
       <c r="W7" t="n">
+        <v>1.228</v>
+      </c>
+      <c r="X7" t="n">
         <v>0</v>
-      </c>
-      <c r="X7" t="n">
-        <v>-1.228</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.6942</v>
+        <v>-0.3135</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1831</v>
+        <v>0.2426</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.8774</v>
+        <v>-0.5561</v>
       </c>
       <c r="G8" t="n">
         <v>0.132</v>
@@ -1078,13 +1078,13 @@
         <v>1.3511</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2472</v>
+        <v>0.1335</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0727</v>
+        <v>0.1322</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3199</v>
+        <v>0.0013</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. GARCIA IBAÑEZ</t>
+          <t>J. MENDIVIL ODERIZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.548</v>
+        <v>-2.4531</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.7997</v>
+        <v>2.0242</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.7483</v>
+        <v>-4.4773</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.9826</v>
+        <v>2.6309</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.5524</v>
+        <v>-0.3694</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5698</v>
+        <v>3.0003</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1521</v>
+        <v>3.9995</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.5641</v>
+        <v>1.3868</v>
       </c>
       <c r="L9" t="n">
-        <v>0.7161999999999999</v>
+        <v>2.6126</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.1347</v>
+        <v>-1.3685</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.9883</v>
+        <v>-1.7562</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.1464</v>
+        <v>0.3877</v>
       </c>
       <c r="P9" t="n">
-        <v>0.193</v>
+        <v>0.772</v>
       </c>
       <c r="Q9" t="n">
         <v>-0.965</v>
       </c>
       <c r="R9" t="n">
-        <v>1.158</v>
+        <v>1.7371</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2446</v>
+        <v>-0.9019</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0132</v>
+        <v>-0.3539</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2578</v>
+        <v>-0.548</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.5138</v>
+        <v>-4.9541</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>-0.6562</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.5138</v>
+        <v>-4.2979</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. MENDIVIL ODERIZ</t>
+          <t>A. GARCIA IBAÑEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.807</v>
+        <v>-2.4747</v>
       </c>
       <c r="E10" t="n">
-        <v>1.7238</v>
+        <v>-0.9405</v>
       </c>
       <c r="F10" t="n">
-        <v>-4.5309</v>
+        <v>-1.5341</v>
       </c>
       <c r="G10" t="n">
-        <v>2.6309</v>
+        <v>-0.9826</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.3694</v>
+        <v>-1.5524</v>
       </c>
       <c r="I10" t="n">
-        <v>3.0003</v>
+        <v>0.5698</v>
       </c>
       <c r="J10" t="n">
-        <v>3.9995</v>
+        <v>0.1521</v>
       </c>
       <c r="K10" t="n">
-        <v>1.3868</v>
+        <v>-0.5641</v>
       </c>
       <c r="L10" t="n">
-        <v>2.6126</v>
+        <v>0.7161999999999999</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.3685</v>
+        <v>-1.1347</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.7562</v>
+        <v>-0.9883</v>
       </c>
       <c r="O10" t="n">
-        <v>0.3877</v>
+        <v>-0.1464</v>
       </c>
       <c r="P10" t="n">
-        <v>0.772</v>
+        <v>0.193</v>
       </c>
       <c r="Q10" t="n">
         <v>-0.965</v>
       </c>
       <c r="R10" t="n">
-        <v>1.7371</v>
+        <v>1.158</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.2559</v>
+        <v>-0.1712</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6544</v>
+        <v>-0.1276</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.6015</v>
+        <v>-0.0436</v>
       </c>
       <c r="V10" t="n">
-        <v>-4.9541</v>
+        <v>-1.5138</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.6562</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-4.2979</v>
+        <v>-1.5138</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.1873</v>
+        <v>-3.5864</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.1357</v>
+        <v>-0.7758</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.0516</v>
+        <v>-2.8106</v>
       </c>
       <c r="G11" t="n">
         <v>-1.03</v>
@@ -1312,13 +1312,13 @@
         <v>0.772</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5083</v>
+        <v>0.0925</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5354</v>
+        <v>-0.1755</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0271</v>
+        <v>0.268</v>
       </c>
       <c r="V11" t="n">
         <v>-2.4559</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>6.007600000000001</v>
+        <v>6.305000000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>12.8513</v>
+        <v>13.1488</v>
       </c>
       <c r="F12" t="n">
-        <v>-6.844000000000001</v>
+        <v>-6.843800000000001</v>
       </c>
       <c r="G12" t="n">
         <v>13.1777</v>
@@ -1381,7 +1381,7 @@
         <v>-4.9305</v>
       </c>
       <c r="P12" t="n">
-        <v>2.775557561562891e-16</v>
+        <v>3.33066907387547e-16</v>
       </c>
       <c r="Q12" t="n">
         <v>-18.3356</v>
@@ -1390,13 +1390,13 @@
         <v>18.3357</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.9302</v>
+        <v>-1.6327</v>
       </c>
       <c r="T12" t="n">
-        <v>-2.0953</v>
+        <v>-1.7977</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1650999999999996</v>
+        <v>0.165</v>
       </c>
       <c r="V12" t="n">
         <v>-5.24</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.4623</v>
+        <v>4.6091</v>
       </c>
       <c r="E13" t="n">
-        <v>5.6299</v>
+        <v>5.8302</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.1676</v>
+        <v>-1.2212</v>
       </c>
       <c r="G13" t="n">
         <v>-0.7238</v>
@@ -1468,13 +1468,13 @@
         <v>3.6672</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.2578</v>
+        <v>-0.111</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.7006</v>
+        <v>-0.5003</v>
       </c>
       <c r="U13" t="n">
-        <v>0.4428</v>
+        <v>0.3893</v>
       </c>
       <c r="V13" t="n">
         <v>2.7418</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.9121</v>
+        <v>0.9641999999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>3.8166</v>
+        <v>2.8151</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.9045</v>
+        <v>-1.8509</v>
       </c>
       <c r="G14" t="n">
         <v>-1.3267</v>
@@ -1546,13 +1546,13 @@
         <v>2.1231</v>
       </c>
       <c r="S14" t="n">
-        <v>2.0385</v>
+        <v>1.0906</v>
       </c>
       <c r="T14" t="n">
-        <v>1.7186</v>
+        <v>0.7171999999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3199</v>
+        <v>0.3734</v>
       </c>
       <c r="V14" t="n">
         <v>0.0422</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.3089</v>
+        <v>0.7953</v>
       </c>
       <c r="E15" t="n">
-        <v>0.6413</v>
+        <v>-0.0596</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6675</v>
+        <v>0.8549</v>
       </c>
       <c r="G15" t="n">
         <v>1.094</v>
@@ -1624,13 +1624,13 @@
         <v>1.5441</v>
       </c>
       <c r="S15" t="n">
-        <v>0.8216</v>
+        <v>0.308</v>
       </c>
       <c r="T15" t="n">
-        <v>0.7998</v>
+        <v>0.0988</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0218</v>
+        <v>0.2092</v>
       </c>
       <c r="V15" t="n">
         <v>-1.1857</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1921</v>
+        <v>0.2188</v>
       </c>
       <c r="E16" t="n">
         <v>0.0407</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1514</v>
+        <v>0.1781</v>
       </c>
       <c r="G16" t="n">
         <v>0.1742</v>
@@ -1702,13 +1702,13 @@
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0178</v>
+        <v>0.0446</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0178</v>
+        <v>0.0446</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.2065</v>
+        <v>-0.6536999999999999</v>
       </c>
       <c r="E17" t="n">
-        <v>1.6445</v>
+        <v>1.1438</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.851</v>
+        <v>-1.7974</v>
       </c>
       <c r="G17" t="n">
         <v>-2.2817</v>
@@ -1780,13 +1780,13 @@
         <v>1.9301</v>
       </c>
       <c r="S17" t="n">
-        <v>0.5843</v>
+        <v>0.1372</v>
       </c>
       <c r="T17" t="n">
-        <v>0.5619</v>
+        <v>0.0612</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0225</v>
+        <v>0.076</v>
       </c>
       <c r="V17" t="n">
         <v>2.4559</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.5546</v>
+        <v>-1.5209</v>
       </c>
       <c r="E18" t="n">
-        <v>2.1072</v>
+        <v>2.007</v>
       </c>
       <c r="F18" t="n">
-        <v>-3.6618</v>
+        <v>-3.5279</v>
       </c>
       <c r="G18" t="n">
         <v>-3.4856</v>
@@ -1858,13 +1858,13 @@
         <v>1.9301</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3272</v>
+        <v>-0.2935</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1057</v>
+        <v>-0.2059</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2214</v>
+        <v>-0.0876</v>
       </c>
       <c r="V18" t="n">
         <v>0.3281</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.3665</v>
+        <v>-1.7329</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.1034</v>
+        <v>-0.2021</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.2631</v>
+        <v>-1.5308</v>
       </c>
       <c r="G19" t="n">
         <v>1.3477</v>
@@ -1936,13 +1936,13 @@
         <v>2.3161</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2208</v>
+        <v>0.4128</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.8923</v>
+        <v>0.0089</v>
       </c>
       <c r="U19" t="n">
-        <v>0.6715</v>
+        <v>0.4038</v>
       </c>
       <c r="V19" t="n">
         <v>-0.9843</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.7611</v>
+        <v>-2.428</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.835</v>
+        <v>-0.2341</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.9262</v>
+        <v>-2.1939</v>
       </c>
       <c r="G20" t="n">
         <v>-4.5474</v>
@@ -2014,13 +2014,13 @@
         <v>2.7021</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2366</v>
+        <v>0.0965</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7733</v>
+        <v>-0.1725</v>
       </c>
       <c r="U20" t="n">
-        <v>0.5367</v>
+        <v>0.269</v>
       </c>
       <c r="V20" t="n">
         <v>0.2859</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-6.9941</v>
+        <v>-6.2594</v>
       </c>
       <c r="E21" t="n">
-        <v>-5.098</v>
+        <v>-4.4971</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.8962</v>
+        <v>-1.7623</v>
       </c>
       <c r="G21" t="n">
         <v>-3.4282</v>
@@ -2092,13 +2092,13 @@
         <v>2.1231</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4898</v>
+        <v>0.2449</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7733</v>
+        <v>-0.1725</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2835</v>
+        <v>0.4174</v>
       </c>
       <c r="V21" t="n">
         <v>1.5561</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.007400000000001</v>
+        <v>-6.0075</v>
       </c>
       <c r="E22" t="n">
-        <v>6.843800000000001</v>
+        <v>6.8439</v>
       </c>
       <c r="F22" t="n">
-        <v>-12.8515</v>
+        <v>-12.8514</v>
       </c>
       <c r="G22" t="n">
         <v>-13.1775</v>
@@ -2170,10 +2170,10 @@
         <v>18.3359</v>
       </c>
       <c r="S22" t="n">
-        <v>1.93</v>
+        <v>1.9301</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1649000000000004</v>
+        <v>-0.1651</v>
       </c>
       <c r="U22" t="n">
         <v>2.0951</v>
